--- a/fixtures/pgfn/lista-manual.xlsx
+++ b/fixtures/pgfn/lista-manual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\damaz\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CA476F8-4B73-4928-A9AF-125873FB9DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49C5052E-3A5B-4059-8BCA-2C9E97F88C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB8E60DC-E9D1-463A-90F5-714B4C83A492}"/>
   </bookViews>
@@ -983,7 +983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D14347B0-6B68-43B5-BB92-5D3889B0249D}">
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -2323,31 +2323,31 @@
         <v>2101.84</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
         <v>28</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B113" t="s">
         <v>14</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D113" t="s">
         <v>29</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E113" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
         <v>30</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B114" t="s">
         <v>31</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D114" t="s">
         <v>32</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E114" t="s">
         <v>33</v>
       </c>
     </row>

--- a/fixtures/pgfn/lista-manual.xlsx
+++ b/fixtures/pgfn/lista-manual.xlsx
@@ -2,18 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\damaz\AppData\Local\Temp\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49C5052E-3A5B-4059-8BCA-2C9E97F88C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B17F5C39-A7EE-4B0F-B391-CAD435ADA061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FB8E60DC-E9D1-463A-90F5-714B4C83A492}"/>
   </bookViews>
   <sheets>
-    <sheet name="Consulta_Lista_Devedores_2026_0" sheetId="1" r:id="rId1"/>
+    <sheet name="Lista" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
